--- a/Opencart_Test_Scenarios_cases.xlsx
+++ b/Opencart_Test_Scenarios_cases.xlsx
@@ -8,15 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96b6f7c0349ee730/Desktop/opencart/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="468" documentId="13_ncr:1_{F811A939-D2A8-4200-B1C4-CDCF34F28D26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1011D320-B677-4F9A-A603-E08F1510CE38}"/>
+  <xr:revisionPtr revIDLastSave="125" documentId="13_ncr:1_{CB3F7933-5987-4351-8FDF-43B872F451DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C55DD546-53C0-4A3E-A278-64BB34084B34}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="test scenarios" sheetId="1" r:id="rId1"/>
     <sheet name="Register" sheetId="2" r:id="rId2"/>
     <sheet name="Login" sheetId="3" r:id="rId3"/>
     <sheet name="Search " sheetId="4" r:id="rId4"/>
+    <sheet name="Checkout" sheetId="8" r:id="rId5"/>
+    <sheet name="RTM" sheetId="5" r:id="rId6"/>
+    <sheet name="Bugs Report" sheetId="6" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="402" uniqueCount="240">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="321">
   <si>
     <t>Project Name</t>
   </si>
@@ -156,9 +159,6 @@
   </si>
   <si>
     <t>TS_013</t>
-  </si>
-  <si>
-    <t>Verify Oder History Functionality</t>
   </si>
   <si>
     <t>TS_014</t>
@@ -933,12 +933,315 @@
   <si>
     <t>use invalid email</t>
   </si>
+  <si>
+    <t>Opencart(frontend)</t>
+  </si>
+  <si>
+    <t>Client</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mohanapriya </t>
+  </si>
+  <si>
+    <t>Creation Date</t>
+  </si>
+  <si>
+    <t>DD-MM-YYYY</t>
+  </si>
+  <si>
+    <t>Requiretment ID</t>
+  </si>
+  <si>
+    <t>Test Scenario ID</t>
+  </si>
+  <si>
+    <t>Test Scenario Description</t>
+  </si>
+  <si>
+    <t>P0</t>
+  </si>
+  <si>
+    <t>P1</t>
+  </si>
+  <si>
+    <t>P4</t>
+  </si>
+  <si>
+    <t>P2</t>
+  </si>
+  <si>
+    <t>P3</t>
+  </si>
+  <si>
+    <t>Verify Order History Functionality</t>
+  </si>
+  <si>
+    <t>Test case ID</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Defect id</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Bug_001</t>
+  </si>
+  <si>
+    <t>Not Executed</t>
+  </si>
+  <si>
+    <t>Bug ID</t>
+  </si>
+  <si>
+    <t>Description/Summary</t>
+  </si>
+  <si>
+    <t>Steps to Reproduce</t>
+  </si>
+  <si>
+    <t>Severity</t>
+  </si>
+  <si>
+    <t>Screenshot</t>
+  </si>
+  <si>
+    <t>TC_COF_001</t>
+  </si>
+  <si>
+    <t>1.Click on Checkout link</t>
+  </si>
+  <si>
+    <t>Verify Check out navigation with empty shopping cart</t>
+  </si>
+  <si>
+    <t>1.System should Navigate to shopping  Cart page instead of checkout page
+2.System should be show "your shopping cart is empty"</t>
+  </si>
+  <si>
+    <t>1.Launch the application
+2.No product added to cart</t>
+  </si>
+  <si>
+    <t>TC_COF_002</t>
+  </si>
+  <si>
+    <t>TC_COF_003</t>
+  </si>
+  <si>
+    <t>TC_COF_004</t>
+  </si>
+  <si>
+    <t>TC_COF_005</t>
+  </si>
+  <si>
+    <t>TC_COF_006</t>
+  </si>
+  <si>
+    <t>TC_COF_007</t>
+  </si>
+  <si>
+    <t>TC_COF_008</t>
+  </si>
+  <si>
+    <t>TC_COF_009</t>
+  </si>
+  <si>
+    <t>TC_COF_010</t>
+  </si>
+  <si>
+    <t>TC_COF_011</t>
+  </si>
+  <si>
+    <t>TC_COF_012</t>
+  </si>
+  <si>
+    <t>TS_006
+Verify Checkout Functionality</t>
+  </si>
+  <si>
+    <t>Verify check out navigation with Non-empty shopping cart</t>
+  </si>
+  <si>
+    <t>1.Launch the application
+2.add item(s) to shoping cart</t>
+  </si>
+  <si>
+    <t>Verify check out navigation using Shoping cart Link</t>
+  </si>
+  <si>
+    <t>1.Click on Shopping cart Link(ER-1)
+2.Click on Checkout buttion(ER-2)</t>
+  </si>
+  <si>
+    <t>1. System should navigate to Checkout page.
+2.System should display shipping Address form</t>
+  </si>
+  <si>
+    <t>1.System should Navigate to Shopping cart Page with proper details
+2.System should navigate to Checkout page with shipping Address form</t>
+  </si>
+  <si>
+    <t>Verify Check out navigation using CartBlock (minicart)</t>
+  </si>
+  <si>
+    <t>1.Click on item(s) Block 
+2.Click on checkout Link</t>
+  </si>
+  <si>
+    <t>1.System should show proper Product details
+2.System should Navigate to checkout page with shipping Address form</t>
+  </si>
+  <si>
+    <t>Verify Check out navigation with empty shopping cart after successful login</t>
+  </si>
+  <si>
+    <t>Verify check out navigation with Non-empty shopping cart after successful login</t>
+  </si>
+  <si>
+    <t>1.Launch the application
+2.Login the application
+3.add item(s) to shoping cart</t>
+  </si>
+  <si>
+    <t>1.Click on Address book
+2.Fill the Address form
+3.Click on Continue
+4.Click on checkout link</t>
+  </si>
+  <si>
+    <t>1.Launch the application
+2.Login with valid credentials
+2.No product added to cart</t>
+  </si>
+  <si>
+    <t>Verify Check out Navigation with Newly added Address</t>
+  </si>
+  <si>
+    <t>1.Launch the application
+2.Login with valid credentials 
+3.add item(s) to shoping cart</t>
+  </si>
+  <si>
+    <t>1.System should display Address books Entries 
+2.System should show success message after adding address.
+3.System should navigate to checkout page with shipping Address form</t>
+  </si>
+  <si>
+    <t>1.Launch the application
+2.add item(s) to shoping cart</t>
+  </si>
+  <si>
+    <t>1.Click on Checkout link
+2. Observe URL,Title,Breadcrumb</t>
+  </si>
+  <si>
+    <t>1.System should display Proper URL,Title, Breadcrumb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify checkout navigation Breadcrumb , URL, Title </t>
+  </si>
+  <si>
+    <t>Verify checkout navigation Breadcrumb , URL, Title after Login</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.System should display correct check URL </t>
+  </si>
+  <si>
+    <t>1.Click on checkout Link</t>
+  </si>
+  <si>
+    <t>Verify Check out Navigation with Existing address after login</t>
+  </si>
+  <si>
+    <t>1.Launch the application
+2.Login with valid credentials 
+3.add item(s) to shoping cart
+4.user has a saved address</t>
+  </si>
+  <si>
+    <t>1.Click on checkout Link
+2.Click on I want to use an existing Address
+3.select Existing address use drop down
+4.click shipping method choose button
+5.Click on continue
+6.Click on payment method choose button
+7.Click on continue 
+8.Click on confirm order</t>
+  </si>
+  <si>
+    <t>Verify Check out Navigation with Existing address after login and place order</t>
+  </si>
+  <si>
+    <t>1.System should navigate the checkout page with existing shipping Address</t>
+  </si>
+  <si>
+    <t>1.System should navigate the checkout page with Enable to use existing shipping address
+2.System should allow Selction of shipping method
+3.System should allow Selection of payment method
+4.Order should be placed succeesfully 
+5.System should display order confirmation Message</t>
+  </si>
+  <si>
+    <t>Verify Check and place order  without login</t>
+  </si>
+  <si>
+    <t>1.Launch the application.
+2.Add Product(s) to shoping cart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.Click on checkout Link
+2.Click on guest Checkout button.
+3.Fill the mandatory Field
+4.Click on continue
+5.Click shipping method choose button
+6.click on continue
+7.Click on payment method choose button
+8.Click on continue
+9.click on confirm order button
+</t>
+  </si>
+  <si>
+    <t>1.System should navigate to checkout page
+2. system should allow to the fill the personal details form
+3.System should allow Selction of shipping method
+4.System should allow Selection of payment method
+5.Order should be placed succeesfully 
+6.System should display order confirmation Message</t>
+  </si>
+  <si>
+    <t>B_001</t>
+  </si>
+  <si>
+    <t>1.Open the Application URL
+2.Click on My Account drop Menu
+3.Click on Login
+4.Click Forgotten Password link
+5.Enter Valid Register Email Address
+6.Click on Continue Button</t>
+  </si>
+  <si>
+    <t>Confirmation message not showed</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>1.Account created successfully
+2.redirected to the Account page</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -967,6 +1270,35 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFFFF00"/>
+      <name val="Verdana"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -994,7 +1326,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -1017,12 +1349,67 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -1031,9 +1418,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1049,12 +1433,68 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="1">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1334,74 +1774,81 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D27"/>
+  <dimension ref="A1:E27"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.44140625" customWidth="1"/>
     <col min="2" max="2" width="17.5546875" customWidth="1"/>
     <col min="3" max="3" width="38.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.88671875" customWidth="1"/>
+    <col min="4" max="4" width="38.33203125" customWidth="1"/>
+    <col min="5" max="5" width="19.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A1" s="5" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5"/>
+      <c r="B1" s="24"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D1" s="1"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="E1" s="1"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="5"/>
+      <c r="B2" s="24"/>
       <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="1"/>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="E2" s="1"/>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="24" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5"/>
+      <c r="B3" s="24"/>
       <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D3" s="1"/>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A4" s="5" t="s">
+      <c r="E3" s="1"/>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="5"/>
+      <c r="B4" s="24"/>
       <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D4" s="1"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5" s="5" t="s">
+      <c r="E4" s="1"/>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="5"/>
+      <c r="B5" s="24"/>
       <c r="C5" s="2">
         <v>46093</v>
       </c>
-      <c r="D5" s="1"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6" s="5" t="s">
+      <c r="D5" s="2"/>
+      <c r="E5" s="1"/>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="5"/>
+      <c r="B6" s="24"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6" s="1"/>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>10</v>
       </c>
@@ -1412,10 +1859,13 @@
         <v>12</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>14</v>
       </c>
@@ -1425,11 +1875,14 @@
       <c r="C8" t="s">
         <v>15</v>
       </c>
-      <c r="D8">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D8" t="s">
+        <v>247</v>
+      </c>
+      <c r="E8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>16</v>
       </c>
@@ -1439,11 +1892,14 @@
       <c r="C9" t="s">
         <v>17</v>
       </c>
-      <c r="D9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D9" t="s">
+        <v>247</v>
+      </c>
+      <c r="E9">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -1453,11 +1909,14 @@
       <c r="C10" t="s">
         <v>19</v>
       </c>
-      <c r="D10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D10" t="s">
+        <v>248</v>
+      </c>
+      <c r="E10">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>20</v>
       </c>
@@ -1465,13 +1924,14 @@
         <v>5</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>52</v>
+      </c>
+      <c r="D11" t="s">
+        <v>247</v>
+      </c>
+      <c r="E11" s="16"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>22</v>
       </c>
@@ -1481,11 +1941,11 @@
       <c r="C12" t="s">
         <v>23</v>
       </c>
-      <c r="D12">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>24</v>
       </c>
@@ -1495,11 +1955,11 @@
       <c r="C13" t="s">
         <v>25</v>
       </c>
-      <c r="D13">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D13" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>26</v>
       </c>
@@ -1509,11 +1969,11 @@
       <c r="C14" t="s">
         <v>27</v>
       </c>
-      <c r="D14">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D14" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>28</v>
       </c>
@@ -1523,11 +1983,11 @@
       <c r="C15" t="s">
         <v>29</v>
       </c>
-      <c r="D15">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="D15" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>30</v>
       </c>
@@ -1537,8 +1997,8 @@
       <c r="C16" t="s">
         <v>31</v>
       </c>
-      <c r="D16">
-        <v>10</v>
+      <c r="D16" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -1551,8 +2011,8 @@
       <c r="C17" t="s">
         <v>33</v>
       </c>
-      <c r="D17">
-        <v>10</v>
+      <c r="D17" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -1565,8 +2025,8 @@
       <c r="C18" t="s">
         <v>35</v>
       </c>
-      <c r="D18">
-        <v>10</v>
+      <c r="D18" t="s">
+        <v>247</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -1579,8 +2039,8 @@
       <c r="C19" t="s">
         <v>37</v>
       </c>
-      <c r="D19">
-        <v>10</v>
+      <c r="D19" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -1591,108 +2051,108 @@
         <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20">
-        <v>10</v>
+        <v>252</v>
+      </c>
+      <c r="D20" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B21" t="s">
         <v>5</v>
       </c>
       <c r="C21" t="s">
-        <v>41</v>
-      </c>
-      <c r="D21">
-        <v>10</v>
+        <v>40</v>
+      </c>
+      <c r="D21" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B22" t="s">
         <v>5</v>
       </c>
       <c r="C22" t="s">
-        <v>43</v>
-      </c>
-      <c r="D22">
-        <v>10</v>
+        <v>42</v>
+      </c>
+      <c r="D22" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B23" t="s">
         <v>5</v>
       </c>
       <c r="C23" t="s">
-        <v>45</v>
-      </c>
-      <c r="D23">
-        <v>10</v>
+        <v>44</v>
+      </c>
+      <c r="D23" t="s">
+        <v>251</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B24" t="s">
         <v>5</v>
       </c>
       <c r="C24" t="s">
-        <v>47</v>
-      </c>
-      <c r="D24">
-        <v>10</v>
+        <v>46</v>
+      </c>
+      <c r="D24" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B25" t="s">
         <v>5</v>
       </c>
       <c r="C25" t="s">
-        <v>49</v>
-      </c>
-      <c r="D25">
-        <v>10</v>
+        <v>48</v>
+      </c>
+      <c r="D25" t="s">
+        <v>248</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B26" t="s">
         <v>5</v>
       </c>
       <c r="C26" t="s">
-        <v>51</v>
-      </c>
-      <c r="D26">
-        <v>10</v>
+        <v>50</v>
+      </c>
+      <c r="D26" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B27" t="s">
         <v>5</v>
       </c>
       <c r="C27" t="s">
-        <v>53</v>
-      </c>
-      <c r="D27">
-        <v>10</v>
+        <v>21</v>
+      </c>
+      <c r="D27" t="s">
+        <v>249</v>
       </c>
     </row>
   </sheetData>
@@ -1717,422 +2177,423 @@
     <col min="2" max="2" width="20.44140625" customWidth="1"/>
     <col min="3" max="3" width="21.6640625" customWidth="1"/>
     <col min="4" max="4" width="29.44140625" customWidth="1"/>
-    <col min="5" max="6" width="30" customWidth="1"/>
+    <col min="5" max="5" width="36.21875" customWidth="1"/>
+    <col min="6" max="6" width="30" customWidth="1"/>
     <col min="7" max="7" width="39.6640625" customWidth="1"/>
-    <col min="8" max="8" width="21.6640625" customWidth="1"/>
-    <col min="9" max="9" width="9.6640625" customWidth="1"/>
+    <col min="8" max="8" width="35.88671875" customWidth="1"/>
+    <col min="9" max="9" width="27.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="E1" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>320</v>
+      </c>
+      <c r="I2" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C3" s="8" t="s">
         <v>70</v>
       </c>
-      <c r="D1" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C2" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E3" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="H3" s="7"/>
+      <c r="I3" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="J3" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>89</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="G2" s="8" t="s">
+    </row>
+    <row r="4" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="G4" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="8" t="s">
+      <c r="H4" s="7"/>
+      <c r="I4" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="144" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="H5" s="7"/>
+      <c r="I5" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="144" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="3" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
+      <c r="G6" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="B3" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>72</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>69</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>90</v>
-      </c>
-      <c r="H3" s="7"/>
-      <c r="I3" s="8" t="s">
+      <c r="C7" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="G7" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>74</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>75</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>76</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>91</v>
-      </c>
-      <c r="H4" s="7"/>
-      <c r="I4" s="8" t="s">
+    <row r="8" spans="1:10" ht="144" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="F8" s="6" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="5" spans="1:10" ht="144" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>92</v>
-      </c>
-      <c r="F5" s="7" t="s">
+      <c r="G8" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="144" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>68</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="F10" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="G5" s="8" t="s">
-        <v>93</v>
-      </c>
-      <c r="H5" s="7"/>
-      <c r="I5" s="8" t="s">
+      <c r="G10" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="144" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="F11" s="6" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="6" spans="1:10" ht="144" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>83</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>81</v>
-      </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="8" t="s">
+      <c r="G11" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="F12" s="6" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="7" spans="1:10" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>82</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>88</v>
-      </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="8" t="s">
+      <c r="G12" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" ht="144" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>85</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>94</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>98</v>
-      </c>
-      <c r="H8" s="7"/>
-      <c r="I8" s="8" t="s">
+      <c r="G13" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E14" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="F14" s="6" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="9" spans="1:10" ht="144" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>96</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>97</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>99</v>
-      </c>
-      <c r="H9" s="7" t="s">
+      <c r="G14" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="I9" s="8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>101</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>105</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>239</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="H10" s="7"/>
-      <c r="I10" s="8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" ht="144" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>103</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>104</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>106</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>102</v>
-      </c>
-      <c r="H11" s="7"/>
-      <c r="I11" s="8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>110</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>108</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="H12" s="7"/>
-      <c r="I12" s="8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>113</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>111</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="H13" s="7"/>
-      <c r="I13" s="8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
+    </row>
+    <row r="15" spans="1:10" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C14" s="8" t="s">
-        <v>114</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E14" s="8" t="s">
-        <v>115</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>109</v>
-      </c>
-      <c r="H14" s="7"/>
-      <c r="I14" s="8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
+      <c r="B15" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>64</v>
-      </c>
-      <c r="C15" s="8" t="s">
+      <c r="D15" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="E15" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="D15" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="E15" s="8" t="s">
+      <c r="F15" s="6" t="s">
+        <v>237</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7" t="s">
         <v>119</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>238</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>121</v>
-      </c>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8" t="s">
-        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -2146,384 +2607,416 @@
   <dimension ref="A1:I16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.109375" style="7" customWidth="1"/>
-    <col min="2" max="2" width="23.21875" style="7" customWidth="1"/>
-    <col min="3" max="3" width="32" style="7" customWidth="1"/>
-    <col min="4" max="4" width="33.33203125" style="7" customWidth="1"/>
-    <col min="5" max="5" width="38.5546875" style="7" customWidth="1"/>
-    <col min="6" max="6" width="31" style="7" customWidth="1"/>
-    <col min="7" max="7" width="28.109375" style="7" customWidth="1"/>
-    <col min="8" max="8" width="17.6640625" style="7" customWidth="1"/>
-    <col min="9" max="9" width="6.88671875" style="7" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.109375" customWidth="1"/>
+    <col min="2" max="2" width="23.21875" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
+    <col min="4" max="4" width="33.33203125" customWidth="1"/>
+    <col min="5" max="5" width="38.5546875" customWidth="1"/>
+    <col min="6" max="6" width="31" customWidth="1"/>
+    <col min="7" max="7" width="28.109375" customWidth="1"/>
+    <col min="8" max="8" width="17.6640625" customWidth="1"/>
+    <col min="9" max="9" width="6.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H1" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="2" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="C2" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>126</v>
-      </c>
-      <c r="D2" s="8" t="s">
+      <c r="F2" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="G2" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+    </row>
+    <row r="3" spans="1:9" ht="76.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+    </row>
+    <row r="4" spans="1:9" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+    </row>
+    <row r="5" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+    </row>
+    <row r="6" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="F6" s="6"/>
+      <c r="G6" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+    </row>
+    <row r="7" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+    </row>
+    <row r="8" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F8" s="9" t="s">
+        <v>155</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+    </row>
+    <row r="10" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+    </row>
+    <row r="11" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="I11" s="6"/>
+    </row>
+    <row r="12" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+    </row>
+    <row r="13" spans="1:9" ht="144" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>124</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="76.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>129</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>130</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>132</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>133</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>136</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>137</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>141</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>142</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>157</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>153</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>158</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>154</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>155</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>159</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>156</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>161</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>162</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="B10" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>165</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="E10" s="8" t="s">
-        <v>164</v>
-      </c>
-      <c r="F10" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="C11" s="8" t="s">
+      <c r="G13" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+    </row>
+    <row r="14" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D14" s="7" t="s">
         <v>167</v>
       </c>
-      <c r="D11" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="F11" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>170</v>
-      </c>
-      <c r="H11" s="8" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>171</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>173</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>174</v>
-      </c>
-      <c r="F12" s="11" t="s">
-        <v>156</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="144" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>176</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="E13" s="8" t="s">
-        <v>177</v>
-      </c>
-      <c r="F13" s="8" t="s">
-        <v>125</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="B14" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="C14" s="8" t="s">
+      <c r="E14" s="7" t="s">
         <v>179</v>
       </c>
-      <c r="D14" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="E14" s="8" t="s">
+      <c r="F14" s="6"/>
+      <c r="G14" s="7" t="s">
         <v>180</v>
       </c>
-      <c r="G14" s="8" t="s">
+      <c r="H14" s="6"/>
+      <c r="I14" s="6"/>
+    </row>
+    <row r="15" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="7" t="s">
+      <c r="B15" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>184</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="F15" s="6"/>
+      <c r="G15" s="7" t="s">
+        <v>185</v>
+      </c>
+      <c r="H15" s="6"/>
+      <c r="I15" s="6"/>
+    </row>
+    <row r="16" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="C15" s="8" t="s">
-        <v>185</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="E15" s="8" t="s">
-        <v>184</v>
-      </c>
-      <c r="G15" s="8" t="s">
+      <c r="B16" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="C16" s="8" t="s">
+      <c r="D16" s="7" t="s">
         <v>187</v>
       </c>
-      <c r="D16" s="8" t="s">
+      <c r="E16" s="7" t="s">
         <v>188</v>
       </c>
-      <c r="E16" s="8" t="s">
+      <c r="F16" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="G16" s="7" t="s">
         <v>189</v>
       </c>
-      <c r="F16" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>190</v>
-      </c>
+      <c r="H16" s="6"/>
+      <c r="I16" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -2554,336 +3047,1360 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="C1" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>70</v>
-      </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H1" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="I1" s="6" t="s">
-        <v>60</v>
-      </c>
     </row>
     <row r="2" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="C2" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="C2" s="8" t="s">
+      <c r="D2" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>221</v>
+      </c>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+    </row>
+    <row r="3" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="B3" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>218</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="F3" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+    </row>
+    <row r="4" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>211</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+    </row>
+    <row r="5" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>219</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>193</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="G5" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+    </row>
+    <row r="6" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>217</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>220</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>221</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+    </row>
+    <row r="7" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>214</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>197</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>196</v>
+      </c>
+      <c r="G7" s="7" t="s">
         <v>222</v>
       </c>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-    </row>
-    <row r="3" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="C3" s="8" t="s">
-        <v>196</v>
-      </c>
-      <c r="D3" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="E3" s="8" t="s">
-        <v>219</v>
-      </c>
-      <c r="F3" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="G3" s="8" t="s">
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+    </row>
+    <row r="8" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>215</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>216</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>199</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>200</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+    </row>
+    <row r="10" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C10" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="H3" s="7"/>
-      <c r="I3" s="7"/>
-    </row>
-    <row r="4" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
-        <v>202</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>212</v>
-      </c>
-      <c r="D4" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="E4" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="F4" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="G4" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
-    </row>
-    <row r="5" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="7" t="s">
-        <v>203</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="C5" s="8" t="s">
-        <v>220</v>
-      </c>
-      <c r="D5" s="8" t="s">
-        <v>194</v>
-      </c>
-      <c r="E5" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="F5" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="G5" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-    </row>
-    <row r="6" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="7" t="s">
-        <v>204</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="C6" s="8" t="s">
+      <c r="D10" s="7" t="s">
         <v>213</v>
       </c>
-      <c r="D6" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="E6" s="8" t="s">
-        <v>218</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>221</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>222</v>
-      </c>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-    </row>
-    <row r="7" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="7" t="s">
-        <v>205</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>215</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="E7" s="8" t="s">
-        <v>198</v>
-      </c>
-      <c r="F7" s="8" t="s">
-        <v>197</v>
-      </c>
-      <c r="G7" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-    </row>
-    <row r="8" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="7" t="s">
-        <v>206</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="E8" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-    </row>
-    <row r="9" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="7" t="s">
-        <v>207</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="C9" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="E9" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>223</v>
-      </c>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-    </row>
-    <row r="10" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+      <c r="E10" s="7" t="s">
+        <v>224</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>225</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+    </row>
+    <row r="11" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
         <v>208</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>224</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>214</v>
-      </c>
-      <c r="E10" s="8" t="s">
+      <c r="B11" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>228</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>229</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+    </row>
+    <row r="12" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>231</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>235</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>236</v>
+      </c>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+    </row>
+    <row r="13" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>191</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>227</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>233</v>
+      </c>
+      <c r="F13" s="7" t="s">
         <v>225</v>
       </c>
-      <c r="F10" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-    </row>
-    <row r="11" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="7" t="s">
-        <v>209</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="C11" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="E11" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="F11" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="G11" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-    </row>
-    <row r="12" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A12" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="D12" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="E12" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="F12" s="8" t="s">
-        <v>160</v>
-      </c>
-      <c r="G12" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-    </row>
-    <row r="13" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="7" t="s">
-        <v>211</v>
-      </c>
-      <c r="B13" s="8" t="s">
-        <v>192</v>
-      </c>
-      <c r="C13" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="E13" s="8" t="s">
+      <c r="G13" s="7" t="s">
         <v>234</v>
       </c>
-      <c r="F13" s="8" t="s">
-        <v>226</v>
-      </c>
-      <c r="G13" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{37599E19-AA35-4603-A6EC-FB08863F3B8B}">
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.88671875" customWidth="1"/>
+    <col min="2" max="2" width="16.77734375" customWidth="1"/>
+    <col min="3" max="3" width="24.6640625" customWidth="1"/>
+    <col min="4" max="4" width="36.109375" customWidth="1"/>
+    <col min="5" max="5" width="35.88671875" customWidth="1"/>
+    <col min="6" max="6" width="14.44140625" customWidth="1"/>
+    <col min="7" max="7" width="24.88671875" customWidth="1"/>
+    <col min="8" max="8" width="19.21875" customWidth="1"/>
+    <col min="9" max="9" width="35.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="G1" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="H1" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A2" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>267</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>269</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+    </row>
+    <row r="3" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>282</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="G3" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="H3" s="20"/>
+      <c r="I3" s="6"/>
+    </row>
+    <row r="4" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>284</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>285</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>287</v>
+      </c>
+      <c r="H4" s="20"/>
+      <c r="I4" s="6"/>
+    </row>
+    <row r="5" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>283</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>289</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="G5" s="4" t="s">
+        <v>290</v>
+      </c>
+      <c r="I5" s="6"/>
+    </row>
+    <row r="6" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>291</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="F6" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="G6" s="7" t="s">
+        <v>268</v>
+      </c>
+      <c r="I6" s="6"/>
+    </row>
+    <row r="7" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>292</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>293</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>266</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="G7" s="21" t="s">
+        <v>286</v>
+      </c>
+      <c r="I7" s="6"/>
+    </row>
+    <row r="8" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>296</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>298</v>
+      </c>
+      <c r="H8" s="6"/>
+      <c r="I8" s="6"/>
+    </row>
+    <row r="9" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>276</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>302</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>299</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>304</v>
+      </c>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+    </row>
+    <row r="10" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
+        <v>277</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>303</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>297</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>301</v>
+      </c>
+      <c r="H10" s="6"/>
+      <c r="I10" s="6"/>
+    </row>
+    <row r="11" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>278</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>306</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>305</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>310</v>
+      </c>
+      <c r="H11" s="6"/>
+      <c r="I11" s="6"/>
+    </row>
+    <row r="12" spans="1:9" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>309</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>307</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>308</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>237</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>311</v>
+      </c>
+      <c r="H12" s="6"/>
+      <c r="I12" s="6"/>
+    </row>
+    <row r="13" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
+        <v>280</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>281</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7" t="s">
+        <v>315</v>
+      </c>
+      <c r="H13" s="6"/>
+      <c r="I13" s="6"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D3377ED-C59C-4E36-9B16-349D1D010550}">
+  <dimension ref="A2:F50"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="32" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" style="11" customWidth="1"/>
+    <col min="3" max="4" width="40.5546875" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" customWidth="1"/>
+    <col min="6" max="6" width="23.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="A2" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="13" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="A3" s="12" t="s">
+        <v>240</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="A4" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="13"/>
+    </row>
+    <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="A5" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="13" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="A6" s="12" t="s">
+        <v>242</v>
+      </c>
+      <c r="B6" s="14">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="A7" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="13" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="A9" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="B9" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>246</v>
+      </c>
+      <c r="D9" s="12" t="s">
+        <v>253</v>
+      </c>
+      <c r="E9" s="12" t="s">
+        <v>254</v>
+      </c>
+      <c r="F9" s="12" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="26">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="B10" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F10" s="6"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="26"/>
+      <c r="B11" s="26"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F11" s="6"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="26"/>
+      <c r="B12" s="26"/>
+      <c r="C12" s="25"/>
+      <c r="D12" s="6" t="s">
+        <v>72</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F12" s="6"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="26"/>
+      <c r="B13" s="26"/>
+      <c r="C13" s="25"/>
+      <c r="D13" s="6" t="s">
+        <v>76</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="26"/>
+      <c r="B14" s="26"/>
+      <c r="C14" s="25"/>
+      <c r="D14" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F14" s="6"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="26"/>
+      <c r="B15" s="26"/>
+      <c r="C15" s="25"/>
+      <c r="D15" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F15" s="6"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="26"/>
+      <c r="B16" s="26"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F16" s="6"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="26"/>
+      <c r="B17" s="26"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="6" t="s">
+        <v>94</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F17" s="6"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="26"/>
+      <c r="B18" s="26"/>
+      <c r="C18" s="25"/>
+      <c r="D18" s="6" t="s">
+        <v>99</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F18" s="6"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="26"/>
+      <c r="B19" s="26"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F19" s="6"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="26"/>
+      <c r="B20" s="26"/>
+      <c r="C20" s="25"/>
+      <c r="D20" s="6" t="s">
+        <v>109</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F20" s="6"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="26"/>
+      <c r="B21" s="26"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="26"/>
+      <c r="B22" s="26"/>
+      <c r="C22" s="25"/>
+      <c r="D22" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F22" s="6"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A23" s="26"/>
+      <c r="B23" s="26"/>
+      <c r="C23" s="25"/>
+      <c r="D23" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F23" s="6"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A24" s="27">
+        <v>1.2</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="C24" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="D24" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="E24" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F24" s="6"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A25" s="27"/>
+      <c r="B25" s="26"/>
+      <c r="C25" s="25"/>
+      <c r="D25" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="E25" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F25" s="6"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="27"/>
+      <c r="B26" s="26"/>
+      <c r="C26" s="25"/>
+      <c r="D26" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="27"/>
+      <c r="B27" s="26"/>
+      <c r="C27" s="25"/>
+      <c r="D27" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E27" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F27" s="6"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="27"/>
+      <c r="B28" s="26"/>
+      <c r="C28" s="25"/>
+      <c r="D28" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F28" s="6"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="27"/>
+      <c r="B29" s="26"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F29" s="6"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="27"/>
+      <c r="B30" s="26"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F30" s="6"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="27"/>
+      <c r="B31" s="26"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E31" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F31" s="6"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="27"/>
+      <c r="B32" s="26"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E32" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="27"/>
+      <c r="B33" s="26"/>
+      <c r="C33" s="25"/>
+      <c r="D33" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="E33" s="6" t="s">
+        <v>256</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="27"/>
+      <c r="B34" s="26"/>
+      <c r="C34" s="25"/>
+      <c r="D34" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F34" s="6"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="27"/>
+      <c r="B35" s="26"/>
+      <c r="C35" s="25"/>
+      <c r="D35" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="E35" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F35" s="6"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="27"/>
+      <c r="B36" s="26"/>
+      <c r="C36" s="25"/>
+      <c r="D36" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="E36" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F36" s="6"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="27"/>
+      <c r="B37" s="26"/>
+      <c r="C37" s="25"/>
+      <c r="D37" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="E37" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F37" s="6"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="27"/>
+      <c r="B38" s="26"/>
+      <c r="C38" s="25"/>
+      <c r="D38" s="6" t="s">
+        <v>182</v>
+      </c>
+      <c r="E38" s="6" t="s">
+        <v>257</v>
+      </c>
+      <c r="F38" s="6"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="27">
+        <v>1.3</v>
+      </c>
+      <c r="B39" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="C39" s="25" t="s">
+        <v>19</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>190</v>
+      </c>
+      <c r="E39" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F39" s="6"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="27"/>
+      <c r="B40" s="26"/>
+      <c r="C40" s="25"/>
+      <c r="D40" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E40" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F40" s="6"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="27"/>
+      <c r="B41" s="26"/>
+      <c r="C41" s="25"/>
+      <c r="D41" s="6" t="s">
+        <v>201</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F41" s="6"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="27"/>
+      <c r="B42" s="26"/>
+      <c r="C42" s="25"/>
+      <c r="D42" s="6" t="s">
+        <v>202</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F42" s="6"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="27"/>
+      <c r="B43" s="26"/>
+      <c r="C43" s="25"/>
+      <c r="D43" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F43" s="6"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="27"/>
+      <c r="B44" s="26"/>
+      <c r="C44" s="25"/>
+      <c r="D44" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F44" s="6"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="27"/>
+      <c r="B45" s="26"/>
+      <c r="C45" s="25"/>
+      <c r="D45" s="6" t="s">
+        <v>205</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F45" s="6"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="27"/>
+      <c r="B46" s="26"/>
+      <c r="C46" s="25"/>
+      <c r="D46" s="6" t="s">
+        <v>206</v>
+      </c>
+      <c r="E46" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F46" s="6"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="27"/>
+      <c r="B47" s="26"/>
+      <c r="C47" s="25"/>
+      <c r="D47" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F47" s="6"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="27"/>
+      <c r="B48" s="26"/>
+      <c r="C48" s="25"/>
+      <c r="D48" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="E48" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F48" s="6"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="27"/>
+      <c r="B49" s="26"/>
+      <c r="C49" s="25"/>
+      <c r="D49" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="E49" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F49" s="6"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="27"/>
+      <c r="B50" s="26"/>
+      <c r="C50" s="25"/>
+      <c r="D50" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="E50" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="F50" s="6"/>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="C39:C50"/>
+    <mergeCell ref="B39:B50"/>
+    <mergeCell ref="A39:A50"/>
+    <mergeCell ref="C10:C23"/>
+    <mergeCell ref="B10:B23"/>
+    <mergeCell ref="A10:A23"/>
+    <mergeCell ref="A24:A38"/>
+    <mergeCell ref="B24:B38"/>
+    <mergeCell ref="C24:C38"/>
+  </mergeCells>
+  <conditionalFormatting sqref="F11:S11">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{180762BC-2083-4B41-A77F-549E1BC6B946}">
+  <dimension ref="A1:H2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="33.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="29.44140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="24.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="38.6640625" customWidth="1"/>
+    <col min="6" max="6" width="12.88671875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="79.21875" customWidth="1"/>
+    <col min="8" max="8" width="17.21875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="19" customFormat="1" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
+        <v>260</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>261</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>262</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>58</v>
+      </c>
+      <c r="E1" s="18" t="s">
+        <v>60</v>
+      </c>
+      <c r="F1" s="18" t="s">
+        <v>263</v>
+      </c>
+      <c r="G1" s="18" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="18" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="124.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>317</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="E2" s="23" t="s">
+        <v>318</v>
+      </c>
+      <c r="F2" s="23" t="s">
+        <v>319</v>
+      </c>
+      <c r="G2" s="23" t="s">
+        <v>250</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Opencart_Test_Scenarios_cases.xlsx
+++ b/Opencart_Test_Scenarios_cases.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96b6f7c0349ee730/Desktop/opencart/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="125" documentId="13_ncr:1_{CB3F7933-5987-4351-8FDF-43B872F451DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C55DD546-53C0-4A3E-A278-64BB34084B34}"/>
+  <xr:revisionPtr revIDLastSave="263" documentId="13_ncr:1_{CB3F7933-5987-4351-8FDF-43B872F451DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49B853CE-51DC-4367-BB10-47CC8218F7BE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="test scenarios" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="635" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="348">
   <si>
     <t>Project Name</t>
   </si>
@@ -252,9 +252,6 @@
   </si>
   <si>
     <t>Test Case Title</t>
-  </si>
-  <si>
-    <t>Verify Account Registration with All Fields</t>
   </si>
   <si>
     <t>1.Click My Account Drop Menu
@@ -277,9 +274,6 @@
 4.Select Subscribe click box and Privacy Policy
 5.Click Continue(ER-1)
 6.Click Continue again on the success page(ER-2)</t>
-  </si>
-  <si>
-    <t>Existing email</t>
   </si>
   <si>
     <t>TC_RF_004</t>
@@ -341,9 +335,6 @@
   <si>
     <t>1.The system should display the message "Your Account Has been Created".
 2.User should be redirected  to the Account page</t>
-  </si>
-  <si>
-    <t>The warning message should be displayed" E-Main Address is already registered"</t>
   </si>
   <si>
     <t xml:space="preserve">1.Click My Account Drop Menu
@@ -695,18 +686,10 @@
     <t>Verify Reset Password link is received in  register Email</t>
   </si>
   <si>
-    <t xml:space="preserve">User Should Received Password Reset email from Opencart Application
-Email Should contains a reset Paswword Link
-</t>
-  </si>
-  <si>
     <t>Open the Email Application</t>
   </si>
   <si>
     <t>Search for Password reset email from Opencart</t>
-  </si>
-  <si>
-    <t>Nothing happends</t>
   </si>
   <si>
     <t>Verify Login using Keyboard keys(Tab and Enter)</t>
@@ -1233,15 +1216,115 @@
     <t>Low</t>
   </si>
   <si>
+    <t>The warning message should be displayed" E-Mail Address is already registered"</t>
+  </si>
+  <si>
+    <t>Warning message displayed"E-Mail Address is already registered"</t>
+  </si>
+  <si>
+    <t>Account created Sucessfully</t>
+  </si>
+  <si>
+    <t>Proper Warning message displayed</t>
+  </si>
+  <si>
     <t>1.Account created successfully
-2.redirected to the Account page</t>
+2.Redirected to the Account page</t>
+  </si>
+  <si>
+    <t>All proper  warning messages displayed</t>
+  </si>
+  <si>
+    <t>The system display the correct placeholder text in all the input fields.</t>
+  </si>
+  <si>
+    <t>Use invalid Password( 32 characters)</t>
+  </si>
+  <si>
+    <t>Use invalid Password( 3 characters)</t>
+  </si>
+  <si>
+    <t>Verify Account Registration with all field</t>
+  </si>
+  <si>
+    <t>Existing regisitered email</t>
+  </si>
+  <si>
+    <t>Valid user details(First name Omitted)</t>
+  </si>
+  <si>
+    <t>Valid user details(Last name Omitted)</t>
+  </si>
+  <si>
+    <t>Valid user details(Email Omitted)</t>
+  </si>
+  <si>
+    <t>Valid user details(Password Omitted)</t>
+  </si>
+  <si>
+    <t>Total Test Cases</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>Failed</t>
+  </si>
+  <si>
+    <t>Pass Rate</t>
+  </si>
+  <si>
+    <t>High Priority</t>
+  </si>
+  <si>
+    <t>Medium Priority</t>
+  </si>
+  <si>
+    <t>EXECUTION SUMMARY</t>
+  </si>
+  <si>
+    <t>1.User successfully logged in and Navigated to my Account</t>
+  </si>
+  <si>
+    <t>Link displayed properly</t>
+  </si>
+  <si>
+    <t>Email Address Field displayed properly</t>
+  </si>
+  <si>
+    <t>Success message not displayed</t>
+  </si>
+  <si>
+    <t>Email Received from Opencart 
+Email contains a reset Password Link</t>
+  </si>
+  <si>
+    <t xml:space="preserve">User Should Received Password Reset email from Opencart Application
+Email Should contains a reset Password Link
+</t>
+  </si>
+  <si>
+    <t>Login Successfully using only keyboard keys</t>
+  </si>
+  <si>
+    <t>Proper Placeholder text displayed</t>
+  </si>
+  <si>
+    <t>Loged out successfully</t>
+  </si>
+  <si>
+    <t>Login Functionality work correctly in all the supported environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Verify Checkout Functionality</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1299,8 +1382,20 @@
       <name val="Verdana"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1325,8 +1420,24 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEEAF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1396,7 +1507,24 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color rgb="FFBBBBBB"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBBBBBB"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBBBBBB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBBBBBB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -1404,12 +1532,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="14" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
@@ -1423,9 +1564,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1445,15 +1583,6 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1462,9 +1591,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1476,6 +1602,49 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1785,10 +1954,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="24"/>
+      <c r="B1" s="19"/>
       <c r="C1" s="1" t="s">
         <v>1</v>
       </c>
@@ -1796,10 +1965,10 @@
       <c r="E1" s="1"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="24"/>
+      <c r="B2" s="19"/>
       <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
@@ -1807,10 +1976,10 @@
       <c r="E2" s="1"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="24" t="s">
+      <c r="A3" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="24"/>
+      <c r="B3" s="19"/>
       <c r="C3" s="1" t="s">
         <v>5</v>
       </c>
@@ -1818,10 +1987,10 @@
       <c r="E3" s="1"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="24" t="s">
+      <c r="A4" s="19" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="24"/>
+      <c r="B4" s="19"/>
       <c r="C4" s="1" t="s">
         <v>7</v>
       </c>
@@ -1829,10 +1998,10 @@
       <c r="E4" s="1"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="24"/>
+      <c r="B5" s="19"/>
       <c r="C5" s="2">
         <v>46093</v>
       </c>
@@ -1840,10 +2009,10 @@
       <c r="E5" s="1"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="24" t="s">
+      <c r="A6" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="24"/>
+      <c r="B6" s="19"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
@@ -1876,7 +2045,7 @@
         <v>15</v>
       </c>
       <c r="D8" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="E8">
         <v>14</v>
@@ -1893,7 +2062,7 @@
         <v>17</v>
       </c>
       <c r="D9" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="E9">
         <v>15</v>
@@ -1910,7 +2079,7 @@
         <v>19</v>
       </c>
       <c r="D10" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="E10">
         <v>12</v>
@@ -1927,9 +2096,9 @@
         <v>52</v>
       </c>
       <c r="D11" t="s">
-        <v>247</v>
-      </c>
-      <c r="E11" s="16"/>
+        <v>242</v>
+      </c>
+      <c r="E11" s="15"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
@@ -1942,7 +2111,7 @@
         <v>23</v>
       </c>
       <c r="D12" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.3">
@@ -1956,7 +2125,7 @@
         <v>25</v>
       </c>
       <c r="D13" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.3">
@@ -1970,7 +2139,7 @@
         <v>27</v>
       </c>
       <c r="D14" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.3">
@@ -1984,7 +2153,7 @@
         <v>29</v>
       </c>
       <c r="D15" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.3">
@@ -1998,7 +2167,7 @@
         <v>31</v>
       </c>
       <c r="D16" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -2012,7 +2181,7 @@
         <v>33</v>
       </c>
       <c r="D17" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -2026,7 +2195,7 @@
         <v>35</v>
       </c>
       <c r="D18" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -2040,7 +2209,7 @@
         <v>37</v>
       </c>
       <c r="D19" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -2051,10 +2220,10 @@
         <v>5</v>
       </c>
       <c r="C20" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="D20" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -2068,7 +2237,7 @@
         <v>40</v>
       </c>
       <c r="D21" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -2082,7 +2251,7 @@
         <v>42</v>
       </c>
       <c r="D22" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -2096,7 +2265,7 @@
         <v>44</v>
       </c>
       <c r="D23" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -2110,7 +2279,7 @@
         <v>46</v>
       </c>
       <c r="D24" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -2124,7 +2293,7 @@
         <v>48</v>
       </c>
       <c r="D25" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -2138,7 +2307,7 @@
         <v>50</v>
       </c>
       <c r="D26" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -2152,7 +2321,7 @@
         <v>21</v>
       </c>
       <c r="D27" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
     </row>
   </sheetData>
@@ -2170,7 +2339,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE726594-8AC3-4AFB-B07A-C00DF8B208FF}">
-  <dimension ref="A1:J15"/>
+  <dimension ref="A1:J24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.77734375" customWidth="1"/>
@@ -2227,16 +2396,16 @@
         <v>65</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="F2" s="7" t="s">
         <v>68</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H2" s="7" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I2" s="7" t="s">
         <v>67</v>
@@ -2249,22 +2418,24 @@
       <c r="B3" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="8" t="s">
-        <v>70</v>
+      <c r="C3" s="7" t="s">
+        <v>324</v>
       </c>
       <c r="D3" s="7" t="s">
         <v>65</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F3" s="7" t="s">
         <v>68</v>
       </c>
       <c r="G3" s="7" t="s">
-        <v>89</v>
-      </c>
-      <c r="H3" s="7"/>
+        <v>87</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>319</v>
+      </c>
       <c r="I3" s="7" t="s">
         <v>67</v>
       </c>
@@ -2272,331 +2443,473 @@
         <v>66</v>
       </c>
     </row>
-    <row r="4" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B4" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D4" s="7" t="s">
         <v>65</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>75</v>
+        <v>325</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="H4" s="7"/>
+        <v>315</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>316</v>
+      </c>
       <c r="I4" s="7" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:10" ht="144" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>65</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F5" s="6" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="H5" s="7"/>
+        <v>89</v>
+      </c>
+      <c r="H5" s="7" t="s">
+        <v>320</v>
+      </c>
       <c r="I5" s="7" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="144" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D6" s="7" t="s">
         <v>65</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F6" s="6" t="s">
         <v>68</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>80</v>
-      </c>
-      <c r="H6" s="7"/>
+        <v>78</v>
+      </c>
+      <c r="H6" s="7" t="s">
+        <v>317</v>
+      </c>
       <c r="I6" s="7" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D7" s="7" t="s">
         <v>65</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>68</v>
       </c>
       <c r="G7" s="7" t="s">
-        <v>87</v>
-      </c>
-      <c r="H7" s="7"/>
+        <v>85</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>318</v>
+      </c>
       <c r="I7" s="7" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="144" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D8" s="7" t="s">
         <v>65</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>68</v>
+        <v>90</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>326</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>97</v>
-      </c>
-      <c r="H8" s="7"/>
+        <v>94</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>318</v>
+      </c>
       <c r="I8" s="7" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="144" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B9" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="D9" s="7" t="s">
         <v>65</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>68</v>
+        <v>93</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>327</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="H9" s="7"/>
+        <v>95</v>
+      </c>
+      <c r="H9" s="7" t="s">
+        <v>318</v>
+      </c>
       <c r="I9" s="7" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="B10" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="D10" s="7" t="s">
         <v>65</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="H10" s="7"/>
+        <v>98</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>318</v>
+      </c>
       <c r="I10" s="7" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="144" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B11" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="D11" s="7" t="s">
         <v>65</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>68</v>
+        <v>328</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>101</v>
-      </c>
-      <c r="H11" s="7"/>
+        <v>98</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>318</v>
+      </c>
       <c r="I11" s="7" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="12" spans="1:10" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="B12" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="D12" s="7" t="s">
         <v>65</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>107</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>68</v>
+        <v>104</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>329</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="H12" s="7"/>
+        <v>105</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>318</v>
+      </c>
       <c r="I12" s="7" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="13" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="B13" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="D13" s="7" t="s">
         <v>65</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>68</v>
+        <v>323</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="H13" s="7"/>
+        <v>105</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>318</v>
+      </c>
       <c r="I13" s="7" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="14" spans="1:10" ht="129.6" x14ac:dyDescent="0.3">
       <c r="A14" s="6" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="B14" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="D14" s="7" t="s">
         <v>65</v>
       </c>
       <c r="E14" s="7" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>68</v>
+        <v>322</v>
       </c>
       <c r="G14" s="7" t="s">
-        <v>108</v>
-      </c>
-      <c r="H14" s="7"/>
+        <v>105</v>
+      </c>
+      <c r="H14" s="7" t="s">
+        <v>318</v>
+      </c>
       <c r="I14" s="7" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="158.4" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" ht="144" x14ac:dyDescent="0.3">
       <c r="A15" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="B15" s="7" t="s">
         <v>63</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="D15" s="7" t="s">
         <v>65</v>
       </c>
       <c r="E15" s="7" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G15" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="H15" s="7"/>
+        <v>117</v>
+      </c>
+      <c r="H15" s="7" t="s">
+        <v>321</v>
+      </c>
       <c r="I15" s="7" t="s">
-        <v>119</v>
+        <v>116</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A16" s="26"/>
+      <c r="B16" s="27"/>
+      <c r="C16" s="27"/>
+      <c r="D16" s="27"/>
+      <c r="E16" s="27"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27"/>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A17" s="26"/>
+      <c r="B17" s="27"/>
+      <c r="C17" s="27"/>
+      <c r="D17" s="27"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="27"/>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A18" s="25" t="s">
+        <v>336</v>
+      </c>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="24"/>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="23" t="s">
+        <v>330</v>
+      </c>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="30">
+        <v>14</v>
+      </c>
+      <c r="F19" s="28"/>
+      <c r="G19" s="28"/>
+      <c r="H19" s="28"/>
+      <c r="I19" s="28"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="23" t="s">
+        <v>331</v>
+      </c>
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="30">
+        <v>14</v>
+      </c>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="28"/>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="23" t="s">
+        <v>333</v>
+      </c>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="23" t="s">
+        <v>334</v>
+      </c>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="23" t="s">
+        <v>335</v>
+      </c>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A18:I18"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A24:D24"/>
+  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2604,7 +2917,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD9202CD-B454-44D2-A40C-0DA0A9565FA4}">
-  <dimension ref="A1:I16"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.109375" customWidth="1"/>
@@ -2614,11 +2927,11 @@
     <col min="5" max="5" width="38.5546875" customWidth="1"/>
     <col min="6" max="6" width="31" customWidth="1"/>
     <col min="7" max="7" width="28.109375" customWidth="1"/>
-    <col min="8" max="8" width="17.6640625" customWidth="1"/>
-    <col min="9" max="9" width="6.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25" customWidth="1"/>
+    <col min="9" max="9" width="20.88671875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="5" t="s">
         <v>53</v>
       </c>
@@ -2647,378 +2960,532 @@
         <v>59</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="72" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="72" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D2" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E2" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="F2" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C2" s="6" t="s">
+      <c r="G2" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="H2" s="7" t="s">
+        <v>337</v>
+      </c>
+      <c r="I2" s="32" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" ht="76.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="B3" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C3" s="7" t="s">
         <v>126</v>
       </c>
-      <c r="E2" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="G2" s="7" t="s">
+      <c r="D3" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-    </row>
-    <row r="3" spans="1:9" ht="76.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="6" t="s">
+      <c r="E3" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C3" s="7" t="s">
+      <c r="F3" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="G3" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="H3" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="I3" s="32" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="F3" s="7" t="s">
+      <c r="B4" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="D4" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>133</v>
       </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-    </row>
-    <row r="4" spans="1:9" ht="100.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="6" t="s">
+      <c r="F4" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="I4" s="32" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="A5" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C4" s="7" t="s">
+      <c r="B5" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D5" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="G5" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="F4" s="7" t="s">
+      <c r="H5" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="I5" s="32" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="A6" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="G4" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-    </row>
-    <row r="5" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A5" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="D5" s="7" t="s">
+      <c r="B6" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="G6" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="E5" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="F5" s="7" t="s">
+      <c r="H6" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="I6" s="32" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="A7" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="G5" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-    </row>
-    <row r="6" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A6" s="6" t="s">
+      <c r="B7" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="H7" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="I7" s="32" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="A8" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>152</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="H8" s="7" t="s">
+        <v>318</v>
+      </c>
+      <c r="I8" s="32" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="B6" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="D6" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="E6" s="7" t="s">
+      <c r="B9" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>156</v>
       </c>
-      <c r="F6" s="6"/>
-      <c r="G6" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="H6" s="6"/>
-      <c r="I6" s="6"/>
-    </row>
-    <row r="7" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A7" s="6" t="s">
+      <c r="G9" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>338</v>
+      </c>
+      <c r="I9" s="32" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="B7" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C7" s="7" t="s">
+      <c r="B10" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="E10" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="H10" s="7" t="s">
+        <v>339</v>
+      </c>
+      <c r="I10" s="32" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" ht="72" x14ac:dyDescent="0.3">
+      <c r="A11" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="F11" s="9" t="s">
         <v>152</v>
       </c>
-      <c r="D7" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>157</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-    </row>
-    <row r="8" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A8" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>154</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>158</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>133</v>
-      </c>
-      <c r="H8" s="6"/>
-      <c r="I8" s="6"/>
-    </row>
-    <row r="9" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
+      <c r="G11" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="H11" s="7" t="s">
+        <v>340</v>
+      </c>
+      <c r="I11" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="J11" s="31"/>
+    </row>
+    <row r="12" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>160</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>161</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>162</v>
-      </c>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-    </row>
-    <row r="10" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="6" t="s">
+      <c r="B12" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>342</v>
+      </c>
+      <c r="H12" s="7" t="s">
+        <v>341</v>
+      </c>
+      <c r="I12" s="32" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" ht="144" x14ac:dyDescent="0.3">
+      <c r="A13" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="B10" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C10" s="7" t="s">
+      <c r="B13" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="D13" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="D10" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>163</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>165</v>
-      </c>
-      <c r="H10" s="6"/>
-      <c r="I10" s="6"/>
-    </row>
-    <row r="11" spans="1:9" ht="72" x14ac:dyDescent="0.3">
-      <c r="A11" s="6" t="s">
+      <c r="E13" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>343</v>
+      </c>
+      <c r="I13" s="32" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="B11" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>166</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>168</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="H11" s="7" t="s">
+      <c r="B14" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="E14" s="7" t="s">
         <v>174</v>
       </c>
-      <c r="I11" s="6"/>
-    </row>
-    <row r="12" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>170</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>155</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>171</v>
-      </c>
-      <c r="H12" s="6"/>
-      <c r="I12" s="6"/>
-    </row>
-    <row r="13" spans="1:9" ht="144" x14ac:dyDescent="0.3">
-      <c r="A13" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C13" s="7" t="s">
+      <c r="F14" s="6" t="s">
+        <v>232</v>
+      </c>
+      <c r="G14" s="7" t="s">
         <v>175</v>
       </c>
-      <c r="D13" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="E13" s="7" t="s">
+      <c r="H14" s="7" t="s">
+        <v>344</v>
+      </c>
+      <c r="I14" s="32" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="F13" s="7" t="s">
-        <v>124</v>
-      </c>
-      <c r="G13" s="7" t="s">
+      <c r="B15" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="E15" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>180</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="I15" s="32" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A16" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="H13" s="6"/>
-      <c r="I13" s="6"/>
-    </row>
-    <row r="14" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="E14" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="F14" s="6"/>
-      <c r="G14" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="H14" s="6"/>
-      <c r="I14" s="6"/>
-    </row>
-    <row r="15" spans="1:9" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="6" t="s">
+      <c r="B16" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="C16" s="7" t="s">
         <v>181</v>
       </c>
-      <c r="B15" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C15" s="7" t="s">
+      <c r="D16" s="7" t="s">
+        <v>182</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="G16" s="7" t="s">
         <v>184</v>
       </c>
-      <c r="D15" s="7" t="s">
-        <v>167</v>
-      </c>
-      <c r="E15" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="F15" s="6"/>
-      <c r="G15" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6"/>
-    </row>
-    <row r="16" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A16" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>186</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>187</v>
-      </c>
-      <c r="E16" s="7" t="s">
-        <v>188</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>189</v>
-      </c>
-      <c r="H16" s="6"/>
-      <c r="I16" s="6"/>
+      <c r="H16" s="7" t="s">
+        <v>346</v>
+      </c>
+      <c r="I16" s="32" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="25" t="s">
+        <v>336</v>
+      </c>
+      <c r="B19" s="24"/>
+      <c r="C19" s="24"/>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="24"/>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="23" t="s">
+        <v>330</v>
+      </c>
+      <c r="B20" s="24"/>
+      <c r="C20" s="24"/>
+      <c r="D20" s="24"/>
+      <c r="E20" s="33">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="23" t="s">
+        <v>331</v>
+      </c>
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+      <c r="D21" s="24"/>
+      <c r="E21">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="23" t="s">
+        <v>332</v>
+      </c>
+      <c r="B22" s="24"/>
+      <c r="C22" s="24"/>
+      <c r="D22" s="24"/>
+      <c r="E22">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="23" t="s">
+        <v>333</v>
+      </c>
+      <c r="B23" s="24"/>
+      <c r="C23" s="24"/>
+      <c r="D23" s="24"/>
+      <c r="E23" s="34">
+        <f>14/15*100</f>
+        <v>93.333333333333329</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="23" t="s">
+        <v>334</v>
+      </c>
+      <c r="B24" s="24"/>
+      <c r="C24" s="24"/>
+      <c r="D24" s="24"/>
+      <c r="E24">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="23" t="s">
+        <v>335</v>
+      </c>
+      <c r="B25" s="24"/>
+      <c r="C25" s="24"/>
+      <c r="D25" s="24"/>
+      <c r="E25">
+        <v>2</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="A25:D25"/>
+    <mergeCell ref="A19:I19"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A24:D24"/>
+  </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="F7" r:id="rId1" xr:uid="{82D1187E-0660-44CF-94D9-23AB853491DC}"/>
@@ -3032,7 +3499,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE9DF306-8995-4760-9E4A-1A99D56B6645}">
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I15"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.88671875" customWidth="1"/>
@@ -3077,304 +3544,305 @@
     </row>
     <row r="2" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
     </row>
     <row r="3" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>190</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>213</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>195</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>193</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>218</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>196</v>
-      </c>
       <c r="G3" s="7" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="H3" s="6"/>
       <c r="I3" s="6"/>
     </row>
     <row r="4" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="D4" s="7" t="s">
+        <v>188</v>
+      </c>
+      <c r="E4" s="7" t="s">
         <v>193</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>198</v>
-      </c>
       <c r="F4" s="7" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G4" s="7" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="6"/>
     </row>
     <row r="5" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G5" s="7" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
     </row>
     <row r="6" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>207</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="E6" s="7" t="s">
         <v>212</v>
       </c>
-      <c r="D6" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>217</v>
-      </c>
       <c r="F6" s="7" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="6"/>
     </row>
     <row r="7" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>186</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>209</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>208</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>192</v>
+      </c>
+      <c r="F7" s="7" t="s">
         <v>191</v>
       </c>
-      <c r="C7" s="7" t="s">
-        <v>214</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>213</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>197</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>196</v>
-      </c>
       <c r="G7" s="7" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
     </row>
     <row r="8" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
     </row>
     <row r="9" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D9" s="7" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G9" s="7" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="6"/>
     </row>
     <row r="10" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
     </row>
     <row r="11" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="G11" s="7" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
     </row>
     <row r="12" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C12" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>222</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>230</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="G12" s="7" t="s">
         <v>231</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>227</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>235</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>159</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>236</v>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
     </row>
     <row r="13" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="G13" s="7" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
     </row>
+    <row r="15" spans="1:9" ht="24" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3428,295 +3896,295 @@
     </row>
     <row r="2" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A2" s="6" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="E2" s="7" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="F2" s="7" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G2" s="7" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="6"/>
     </row>
     <row r="3" spans="1:9" ht="72" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="B3" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>277</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>278</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="G3" s="17" t="s">
         <v>281</v>
       </c>
-      <c r="C3" s="7" t="s">
-        <v>282</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>283</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="G3" s="21" t="s">
-        <v>286</v>
-      </c>
-      <c r="H3" s="20"/>
+      <c r="H3" s="16"/>
       <c r="I3" s="6"/>
     </row>
     <row r="4" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A4" s="6" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="E4" s="7" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="F4" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="G4" s="22" t="s">
-        <v>287</v>
-      </c>
-      <c r="H4" s="20"/>
+        <v>232</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>282</v>
+      </c>
+      <c r="H4" s="16"/>
       <c r="I4" s="6"/>
     </row>
     <row r="5" spans="1:9" ht="72" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="I5" s="6"/>
     </row>
     <row r="6" spans="1:9" ht="86.4" x14ac:dyDescent="0.3">
       <c r="A6" s="6" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="I6" s="6"/>
     </row>
     <row r="7" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A7" s="6" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B7" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>287</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>288</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>261</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="G7" s="17" t="s">
         <v>281</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>292</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>293</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>266</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="G7" s="21" t="s">
-        <v>286</v>
       </c>
       <c r="I7" s="6"/>
     </row>
     <row r="8" spans="1:9" ht="115.2" x14ac:dyDescent="0.3">
       <c r="A8" s="6" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="E8" s="7" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G8" s="7" t="s">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="6"/>
     </row>
     <row r="9" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A9" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="B9" s="7" t="s">
         <v>276</v>
       </c>
-      <c r="B9" s="7" t="s">
-        <v>281</v>
-      </c>
       <c r="C9" s="7" t="s">
-        <v>302</v>
+        <v>297</v>
       </c>
       <c r="D9" s="7" t="s">
+        <v>294</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>295</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="G9" s="7" t="s">
         <v>299</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>300</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>304</v>
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="6"/>
     </row>
     <row r="10" spans="1:9" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A10" s="6" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>303</v>
+        <v>298</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="E10" s="7" t="s">
-        <v>300</v>
+        <v>295</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G10" s="7" t="s">
-        <v>301</v>
+        <v>296</v>
       </c>
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
     </row>
     <row r="11" spans="1:9" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A11" s="6" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>306</v>
+        <v>301</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E11" s="7" t="s">
+        <v>300</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>232</v>
+      </c>
+      <c r="G11" s="7" t="s">
         <v>305</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>237</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>310</v>
       </c>
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
     </row>
     <row r="12" spans="1:9" ht="187.2" x14ac:dyDescent="0.3">
       <c r="A12" s="6" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>309</v>
+        <v>304</v>
       </c>
       <c r="D12" s="7" t="s">
-        <v>307</v>
+        <v>302</v>
       </c>
       <c r="E12" s="7" t="s">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="F12" s="7" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="G12" s="7" t="s">
-        <v>311</v>
+        <v>306</v>
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
     </row>
     <row r="13" spans="1:9" ht="201.6" x14ac:dyDescent="0.3">
       <c r="A13" s="6" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>312</v>
+        <v>307</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>313</v>
+        <v>308</v>
       </c>
       <c r="E13" s="7" t="s">
-        <v>314</v>
+        <v>309</v>
       </c>
       <c r="F13" s="7"/>
       <c r="G13" s="7" t="s">
-        <v>315</v>
+        <v>310</v>
       </c>
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
@@ -3729,596 +4197,749 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D3377ED-C59C-4E36-9B16-349D1D010550}">
-  <dimension ref="A2:F50"/>
+  <dimension ref="A2:F62"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" style="11" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" style="10" customWidth="1"/>
     <col min="3" max="4" width="40.5546875" customWidth="1"/>
     <col min="5" max="5" width="17.33203125" customWidth="1"/>
     <col min="6" max="6" width="23.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="A2" s="12" t="s">
+      <c r="A2" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="13" t="s">
+      <c r="B2" s="12" t="s">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="A3" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="A4" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="12"/>
+    </row>
+    <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="A5" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="A6" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="B6" s="13">
+        <v>46112</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="A7" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="18" x14ac:dyDescent="0.35">
+      <c r="A9" s="14" t="s">
         <v>239</v>
       </c>
-    </row>
-    <row r="3" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="A3" s="12" t="s">
+      <c r="B9" s="14" t="s">
         <v>240</v>
       </c>
-      <c r="B3" s="13" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="A4" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="13"/>
-    </row>
-    <row r="5" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="A5" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="13" t="s">
+      <c r="C9" s="14" t="s">
         <v>241</v>
       </c>
-    </row>
-    <row r="6" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="A6" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="B6" s="14">
-        <v>46112</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="A7" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="13" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="18" x14ac:dyDescent="0.35">
-      <c r="A9" s="15" t="s">
-        <v>244</v>
-      </c>
-      <c r="B9" s="15" t="s">
-        <v>245</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>246</v>
-      </c>
-      <c r="D9" s="12" t="s">
-        <v>253</v>
-      </c>
-      <c r="E9" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="F9" s="12" t="s">
-        <v>255</v>
+      <c r="D9" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="E9" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="F9" s="11" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="26">
+      <c r="A10" s="21">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B10" s="26" t="s">
+      <c r="B10" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="20" t="s">
         <v>15</v>
       </c>
       <c r="D10" s="6" t="s">
         <v>61</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F10" s="6"/>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="26"/>
-      <c r="B11" s="26"/>
-      <c r="C11" s="25"/>
+      <c r="A11" s="21"/>
+      <c r="B11" s="21"/>
+      <c r="C11" s="20"/>
       <c r="D11" s="6" t="s">
         <v>62</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F11" s="6"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="26"/>
-      <c r="B12" s="26"/>
-      <c r="C12" s="25"/>
+      <c r="A12" s="21"/>
+      <c r="B12" s="21"/>
+      <c r="C12" s="20"/>
       <c r="D12" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="E12" s="6" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F12" s="6"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="26"/>
-      <c r="B13" s="26"/>
-      <c r="C13" s="25"/>
+      <c r="A13" s="21"/>
+      <c r="B13" s="21"/>
+      <c r="C13" s="20"/>
       <c r="D13" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="F13" s="6"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="21"/>
+      <c r="B14" s="21"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="F13" s="6"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="26"/>
-      <c r="B14" s="26"/>
-      <c r="C14" s="25"/>
-      <c r="D14" s="6" t="s">
-        <v>78</v>
-      </c>
       <c r="E14" s="6" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F14" s="6"/>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="26"/>
-      <c r="B15" s="26"/>
-      <c r="C15" s="25"/>
+      <c r="A15" s="21"/>
+      <c r="B15" s="21"/>
+      <c r="C15" s="20"/>
       <c r="D15" s="6" t="s">
+        <v>81</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="F15" s="6"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="21"/>
+      <c r="B16" s="21"/>
+      <c r="C16" s="20"/>
+      <c r="D16" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="E15" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="F15" s="6"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="26"/>
-      <c r="B16" s="26"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="6" t="s">
-        <v>85</v>
-      </c>
       <c r="E16" s="6" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F16" s="6"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="26"/>
-      <c r="B17" s="26"/>
-      <c r="C17" s="25"/>
+      <c r="A17" s="21"/>
+      <c r="B17" s="21"/>
+      <c r="C17" s="20"/>
       <c r="D17" s="6" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F17" s="6"/>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="26"/>
-      <c r="B18" s="26"/>
-      <c r="C18" s="25"/>
+      <c r="A18" s="21"/>
+      <c r="B18" s="21"/>
+      <c r="C18" s="20"/>
       <c r="D18" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="F18" s="6"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="21"/>
+      <c r="B19" s="21"/>
+      <c r="C19" s="20"/>
+      <c r="D19" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="E18" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="F18" s="6"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="26"/>
-      <c r="B19" s="26"/>
-      <c r="C19" s="25"/>
-      <c r="D19" s="6" t="s">
-        <v>102</v>
-      </c>
       <c r="E19" s="6" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F19" s="6"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="26"/>
-      <c r="B20" s="26"/>
-      <c r="C20" s="25"/>
+      <c r="A20" s="21"/>
+      <c r="B20" s="21"/>
+      <c r="C20" s="20"/>
       <c r="D20" s="6" t="s">
+        <v>106</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="F20" s="6"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="21"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="E20" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="F20" s="6"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="26"/>
-      <c r="B21" s="26"/>
-      <c r="C21" s="25"/>
-      <c r="D21" s="6" t="s">
+      <c r="E21" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="F21" s="6"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A22" s="21"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="20"/>
+      <c r="D22" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="E21" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="F21" s="6"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="26"/>
-      <c r="B22" s="26"/>
-      <c r="C22" s="25"/>
-      <c r="D22" s="6" t="s">
-        <v>115</v>
-      </c>
       <c r="E22" s="6" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F22" s="6"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="26"/>
-      <c r="B23" s="26"/>
-      <c r="C23" s="25"/>
+      <c r="A23" s="21"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="20"/>
       <c r="D23" s="6" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="E23" s="6" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F23" s="6"/>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="27">
+      <c r="A24" s="22">
         <v>1.2</v>
       </c>
-      <c r="B24" s="26" t="s">
+      <c r="B24" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="C24" s="25" t="s">
+      <c r="C24" s="20" t="s">
         <v>17</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F24" s="6"/>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="27"/>
-      <c r="B25" s="26"/>
-      <c r="C25" s="25"/>
+      <c r="A25" s="22"/>
+      <c r="B25" s="21"/>
+      <c r="C25" s="20"/>
       <c r="D25" s="6" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="E25" s="6" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F25" s="6"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="27"/>
-      <c r="B26" s="26"/>
-      <c r="C26" s="25"/>
+      <c r="A26" s="22"/>
+      <c r="B26" s="21"/>
+      <c r="C26" s="20"/>
       <c r="D26" s="6" t="s">
+        <v>131</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="F26" s="6"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="22"/>
+      <c r="B27" s="21"/>
+      <c r="C27" s="20"/>
+      <c r="D27" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="E26" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="F26" s="6"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="27"/>
-      <c r="B27" s="26"/>
-      <c r="C27" s="25"/>
-      <c r="D27" s="6" t="s">
-        <v>137</v>
-      </c>
       <c r="E27" s="6" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F27" s="6"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="27"/>
-      <c r="B28" s="26"/>
-      <c r="C28" s="25"/>
+      <c r="A28" s="22"/>
+      <c r="B28" s="21"/>
+      <c r="C28" s="20"/>
       <c r="D28" s="6" t="s">
+        <v>140</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="F28" s="6"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="22"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="20"/>
+      <c r="D29" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="E29" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="F29" s="6"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="22"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="20"/>
+      <c r="D30" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="E30" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="F30" s="6"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="22"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="20"/>
+      <c r="D31" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="E28" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="F28" s="6"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="27"/>
-      <c r="B29" s="26"/>
-      <c r="C29" s="25"/>
-      <c r="D29" s="6" t="s">
+      <c r="E31" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="F31" s="6"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A32" s="22"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="20"/>
+      <c r="D32" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="F29" s="6"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="27"/>
-      <c r="B30" s="26"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="6" t="s">
+      <c r="E32" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="F32" s="6"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A33" s="22"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="20"/>
+      <c r="D33" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="E30" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="F30" s="6"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="27"/>
-      <c r="B31" s="26"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="6" t="s">
+      <c r="E33" s="6" t="s">
+        <v>251</v>
+      </c>
+      <c r="F33" s="6" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="22"/>
+      <c r="B34" s="21"/>
+      <c r="C34" s="20"/>
+      <c r="D34" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="E31" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="F31" s="6"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="27"/>
-      <c r="B32" s="26"/>
-      <c r="C32" s="25"/>
-      <c r="D32" s="6" t="s">
+      <c r="E34" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="F34" s="6"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A35" s="22"/>
+      <c r="B35" s="21"/>
+      <c r="C35" s="20"/>
+      <c r="D35" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="E32" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="F32" s="6"/>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="27"/>
-      <c r="B33" s="26"/>
-      <c r="C33" s="25"/>
-      <c r="D33" s="6" t="s">
+      <c r="E35" s="6" t="s">
+        <v>252</v>
+      </c>
+      <c r="F35" s="6"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="22"/>
+      <c r="B36" s="21"/>
+      <c r="C36" s="20"/>
+      <c r="D36" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="E33" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="27"/>
-      <c r="B34" s="26"/>
-      <c r="C34" s="25"/>
-      <c r="D34" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="E34" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="F34" s="6"/>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="27"/>
-      <c r="B35" s="26"/>
-      <c r="C35" s="25"/>
-      <c r="D35" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="E35" s="6" t="s">
-        <v>257</v>
-      </c>
-      <c r="F35" s="6"/>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="27"/>
-      <c r="B36" s="26"/>
-      <c r="C36" s="25"/>
-      <c r="D36" s="6" t="s">
-        <v>151</v>
-      </c>
       <c r="E36" s="6" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F36" s="6"/>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="27"/>
-      <c r="B37" s="26"/>
-      <c r="C37" s="25"/>
+      <c r="A37" s="22"/>
+      <c r="B37" s="21"/>
+      <c r="C37" s="20"/>
       <c r="D37" s="6" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="E37" s="6" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F37" s="6"/>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="27"/>
-      <c r="B38" s="26"/>
-      <c r="C38" s="25"/>
+      <c r="A38" s="22"/>
+      <c r="B38" s="21"/>
+      <c r="C38" s="20"/>
       <c r="D38" s="6" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F38" s="6"/>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="27">
+      <c r="A39" s="22">
         <v>1.3</v>
       </c>
-      <c r="B39" s="26" t="s">
+      <c r="B39" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="C39" s="25" t="s">
+      <c r="C39" s="20" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="E39" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="F39" s="6"/>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="27"/>
-      <c r="B40" s="26"/>
-      <c r="C40" s="25"/>
+      <c r="A40" s="22"/>
+      <c r="B40" s="21"/>
+      <c r="C40" s="20"/>
       <c r="D40" s="6" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="E40" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="F40" s="6"/>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="27"/>
-      <c r="B41" s="26"/>
-      <c r="C41" s="25"/>
+      <c r="A41" s="22"/>
+      <c r="B41" s="21"/>
+      <c r="C41" s="20"/>
       <c r="D41" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="E41" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F41" s="6"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="22"/>
+      <c r="B42" s="21"/>
+      <c r="C42" s="20"/>
+      <c r="D42" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="E42" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F42" s="6"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="22"/>
+      <c r="B43" s="21"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="6" t="s">
+        <v>198</v>
+      </c>
+      <c r="E43" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F43" s="6"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="22"/>
+      <c r="B44" s="21"/>
+      <c r="C44" s="20"/>
+      <c r="D44" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E44" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F44" s="6"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A45" s="22"/>
+      <c r="B45" s="21"/>
+      <c r="C45" s="20"/>
+      <c r="D45" s="6" t="s">
+        <v>200</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F45" s="6"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A46" s="22"/>
+      <c r="B46" s="21"/>
+      <c r="C46" s="20"/>
+      <c r="D46" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="E41" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="F41" s="6"/>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="27"/>
-      <c r="B42" s="26"/>
-      <c r="C42" s="25"/>
-      <c r="D42" s="6" t="s">
+      <c r="E46" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F46" s="6"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="22"/>
+      <c r="B47" s="21"/>
+      <c r="C47" s="20"/>
+      <c r="D47" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="E42" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="F42" s="6"/>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="27"/>
-      <c r="B43" s="26"/>
-      <c r="C43" s="25"/>
-      <c r="D43" s="6" t="s">
+      <c r="E47" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F47" s="6"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="22"/>
+      <c r="B48" s="21"/>
+      <c r="C48" s="20"/>
+      <c r="D48" s="6" t="s">
         <v>203</v>
       </c>
-      <c r="E43" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="F43" s="6"/>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="27"/>
-      <c r="B44" s="26"/>
-      <c r="C44" s="25"/>
-      <c r="D44" s="6" t="s">
+      <c r="E48" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F48" s="6"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="22"/>
+      <c r="B49" s="21"/>
+      <c r="C49" s="20"/>
+      <c r="D49" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="E44" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="F44" s="6"/>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="27"/>
-      <c r="B45" s="26"/>
-      <c r="C45" s="25"/>
-      <c r="D45" s="6" t="s">
+      <c r="E49" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F49" s="6"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="22"/>
+      <c r="B50" s="21"/>
+      <c r="C50" s="20"/>
+      <c r="D50" s="6" t="s">
         <v>205</v>
       </c>
-      <c r="E45" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="F45" s="6"/>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="27"/>
-      <c r="B46" s="26"/>
-      <c r="C46" s="25"/>
-      <c r="D46" s="6" t="s">
-        <v>206</v>
-      </c>
-      <c r="E46" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="F46" s="6"/>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="27"/>
-      <c r="B47" s="26"/>
-      <c r="C47" s="25"/>
-      <c r="D47" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="E47" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="F47" s="6"/>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="27"/>
-      <c r="B48" s="26"/>
-      <c r="C48" s="25"/>
-      <c r="D48" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="E48" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="F48" s="6"/>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="27"/>
-      <c r="B49" s="26"/>
-      <c r="C49" s="25"/>
-      <c r="D49" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="E49" s="6" t="s">
-        <v>259</v>
-      </c>
-      <c r="F49" s="6"/>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="27"/>
-      <c r="B50" s="26"/>
-      <c r="C50" s="25"/>
-      <c r="D50" s="6" t="s">
-        <v>210</v>
-      </c>
       <c r="E50" s="6" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="F50" s="6"/>
     </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="37">
+        <v>1.4</v>
+      </c>
+      <c r="B51" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="C51" s="37" t="s">
+        <v>347</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>260</v>
+      </c>
+      <c r="E51" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F51" s="6"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="38"/>
+      <c r="B52" s="38"/>
+      <c r="C52" s="38"/>
+      <c r="D52" s="6" t="s">
+        <v>265</v>
+      </c>
+      <c r="E52" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F52" s="6"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="38"/>
+      <c r="B53" s="38"/>
+      <c r="C53" s="38"/>
+      <c r="D53" s="6" t="s">
+        <v>266</v>
+      </c>
+      <c r="E53" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F53" s="6"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="38"/>
+      <c r="B54" s="38"/>
+      <c r="C54" s="38"/>
+      <c r="D54" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="E54" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F54" s="6"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="38"/>
+      <c r="B55" s="38"/>
+      <c r="C55" s="38"/>
+      <c r="D55" s="6" t="s">
+        <v>268</v>
+      </c>
+      <c r="E55" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F55" s="6"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="38"/>
+      <c r="B56" s="38"/>
+      <c r="C56" s="38"/>
+      <c r="D56" s="6" t="s">
+        <v>269</v>
+      </c>
+      <c r="E56" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F56" s="6"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="38"/>
+      <c r="B57" s="38"/>
+      <c r="C57" s="38"/>
+      <c r="D57" s="6" t="s">
+        <v>270</v>
+      </c>
+      <c r="E57" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F57" s="6"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="38"/>
+      <c r="B58" s="38"/>
+      <c r="C58" s="38"/>
+      <c r="D58" s="6" t="s">
+        <v>271</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F58" s="6"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="38"/>
+      <c r="B59" s="38"/>
+      <c r="C59" s="38"/>
+      <c r="D59" s="6" t="s">
+        <v>272</v>
+      </c>
+      <c r="E59" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F59" s="6"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="38"/>
+      <c r="B60" s="38"/>
+      <c r="C60" s="38"/>
+      <c r="D60" s="6" t="s">
+        <v>273</v>
+      </c>
+      <c r="E60" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F60" s="6"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="38"/>
+      <c r="B61" s="38"/>
+      <c r="C61" s="38"/>
+      <c r="D61" s="6" t="s">
+        <v>274</v>
+      </c>
+      <c r="E61" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F61" s="6"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="39"/>
+      <c r="B62" s="39"/>
+      <c r="C62" s="39"/>
+      <c r="D62" s="6" t="s">
+        <v>275</v>
+      </c>
+      <c r="E62" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="F62" s="6"/>
+    </row>
   </sheetData>
-  <mergeCells count="9">
+  <mergeCells count="12">
+    <mergeCell ref="B51:B62"/>
+    <mergeCell ref="A51:A62"/>
+    <mergeCell ref="C51:C62"/>
     <mergeCell ref="C39:C50"/>
     <mergeCell ref="B39:B50"/>
     <mergeCell ref="A39:A50"/>
@@ -4329,6 +4950,7 @@
     <mergeCell ref="B24:B38"/>
     <mergeCell ref="C24:C38"/>
   </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
   <conditionalFormatting sqref="F11:S11">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
@@ -4351,54 +4973,55 @@
     <col min="8" max="8" width="17.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="19" customFormat="1" ht="16.2" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
-        <v>260</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>261</v>
-      </c>
-      <c r="C1" s="18" t="s">
-        <v>262</v>
-      </c>
-      <c r="D1" s="18" t="s">
+    <row r="1" spans="1:8" s="35" customFormat="1" ht="16.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="36" t="s">
+        <v>255</v>
+      </c>
+      <c r="B1" s="36" t="s">
+        <v>256</v>
+      </c>
+      <c r="C1" s="36" t="s">
+        <v>257</v>
+      </c>
+      <c r="D1" s="36" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="F1" s="18" t="s">
-        <v>263</v>
-      </c>
-      <c r="G1" s="18" t="s">
+      <c r="F1" s="36" t="s">
+        <v>258</v>
+      </c>
+      <c r="G1" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="H1" s="18" t="s">
-        <v>264</v>
+      <c r="H1" s="36" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="124.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
-        <v>316</v>
+      <c r="A2" s="6" t="s">
+        <v>311</v>
       </c>
       <c r="B2" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>312</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>166</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>317</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>169</v>
-      </c>
-      <c r="E2" s="23" t="s">
-        <v>318</v>
-      </c>
-      <c r="F2" s="23" t="s">
-        <v>319</v>
-      </c>
-      <c r="G2" s="23" t="s">
-        <v>250</v>
-      </c>
+      <c r="E2" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="F2" s="7" t="s">
+        <v>314</v>
+      </c>
+      <c r="G2" s="7" t="s">
+        <v>245</v>
+      </c>
+      <c r="H2" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
